--- a/artfynd/A 38890-2024 artfynd.xlsx
+++ b/artfynd/A 38890-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,6 +1231,226 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/74799340</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137568826</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57984</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bryggan, Hejholmarna, Horgefjorden, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475812</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6269378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västra Torsås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137568826</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137571816</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58699</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bryggan, Hejholmarna, Horgefjorden, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>475812</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6269378</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Torsås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137571816</t>
         </is>
       </c>
     </row>
@@ -1240,6 +1460,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
